--- a/Result/profitability/2597.xlsx
+++ b/Result/profitability/2597.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM73"/>
+  <dimension ref="A1:AM74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>1.76</v>
       </c>
       <c r="M2" t="n">
-        <v>2.74875</v>
+        <v>2.74</v>
       </c>
       <c r="N2" t="n">
-        <v>16.59375</v>
+        <v>16.71875</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>1.1</v>
       </c>
       <c r="M3" t="n">
-        <v>2.54</v>
+        <v>2.38</v>
       </c>
       <c r="N3" t="n">
-        <v>15.73375</v>
+        <v>15.06625</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.28</v>
       </c>
       <c r="M4" t="n">
-        <v>2.0775</v>
+        <v>2.15</v>
       </c>
       <c r="N4" t="n">
-        <v>13.55125</v>
+        <v>13.61875</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.66</v>
       </c>
       <c r="M5" t="n">
-        <v>1.895</v>
+        <v>1.9325</v>
       </c>
       <c r="N5" t="n">
-        <v>13.28</v>
+        <v>13.30125</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.39</v>
       </c>
       <c r="M6" t="n">
-        <v>1.64375</v>
+        <v>1.59625</v>
       </c>
       <c r="N6" t="n">
-        <v>13.04</v>
+        <v>12.96</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.88</v>
       </c>
       <c r="M7" t="n">
-        <v>1.36875</v>
+        <v>1.26875</v>
       </c>
       <c r="N7" t="n">
-        <v>13.02375</v>
+        <v>12.7775</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>2.16</v>
       </c>
       <c r="M8" t="n">
-        <v>1.20125</v>
+        <v>1.24125</v>
       </c>
       <c r="N8" t="n">
-        <v>14.56625</v>
+        <v>14.45375</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9699,6 +9699,133 @@
       </c>
       <c r="AM73" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2597</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>8759</v>
+      </c>
+      <c r="D74" t="n">
+        <v>7288</v>
+      </c>
+      <c r="E74" t="n">
+        <v>1471</v>
+      </c>
+      <c r="F74" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="G74" t="n">
+        <v>1128</v>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>12.88%</t>
+        </is>
+      </c>
+      <c r="I74" t="n">
+        <v>15</v>
+      </c>
+      <c r="J74" t="n">
+        <v>1143</v>
+      </c>
+      <c r="K74" t="n">
+        <v>838</v>
+      </c>
+      <c r="L74" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="M74" t="n">
+        <v>2.86625</v>
+      </c>
+      <c r="N74" t="n">
+        <v>17.6925</v>
+      </c>
+      <c r="O74" t="n">
+        <v>1</v>
+      </c>
+      <c r="P74" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>0</v>
+      </c>
+      <c r="R74" t="n">
+        <v>0</v>
+      </c>
+      <c r="S74" t="n">
+        <v>1</v>
+      </c>
+      <c r="T74" t="n">
+        <v>0</v>
+      </c>
+      <c r="U74" t="n">
+        <v>1</v>
+      </c>
+      <c r="V74" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W74" t="n">
+        <v>0.3200000000000003</v>
+      </c>
+      <c r="X74" t="n">
+        <v>0.1344537815126052</v>
+      </c>
+      <c r="Y74" t="n">
+        <v>-0.8999999999999986</v>
+      </c>
+      <c r="Z74" t="n">
+        <v>-0.05084745762711862</v>
+      </c>
+      <c r="AA74" t="n">
+        <v>0.3000000000000003</v>
+      </c>
+      <c r="AB74" t="n">
+        <v>0.1250000000000002</v>
+      </c>
+      <c r="AC74" t="n">
+        <v>0.1700000000000017</v>
+      </c>
+      <c r="AD74" t="n">
+        <v>0.01022248947684923</v>
+      </c>
+      <c r="AE74" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF74" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH74" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI74" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK74" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL74" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM74" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
